--- a/data/aroflo_invoicing_report.xlsx
+++ b/data/aroflo_invoicing_report.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J899"/>
+  <dimension ref="A1:J959"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>573.28</v>
+        <v>607.6799999999999</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>281.44</v>
+        <v>312.4</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>624.4299999999999</v>
+        <v>1161.44</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>1167.25</v>
+        <v>875.4400000000001</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>372.17</v>
+        <v>390.78</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>1534.92</v>
+        <v>1719.11</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>698.3</v>
+        <v>740.2</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>818.4299999999999</v>
+        <v>859.35</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>570.62</v>
+        <v>559.21</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="H39" s="3" t="n">
-        <v>399.54</v>
+        <v>743.14</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="H44" s="3" t="n">
-        <v>349.97</v>
+        <v>731.4400000000001</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>478.98</v>
+        <v>517.3</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="H50" s="3" t="n">
-        <v>511.78</v>
+        <v>481.07</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         </is>
       </c>
       <c r="H51" s="3" t="n">
-        <v>226.23</v>
+        <v>253.38</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="H52" s="3" t="n">
-        <v>521.4299999999999</v>
+        <v>1089.79</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="H55" s="3" t="n">
-        <v>2460.03</v>
+        <v>2681.43</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         </is>
       </c>
       <c r="H56" s="3" t="n">
-        <v>324.64</v>
+        <v>175.31</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="H57" s="3" t="n">
-        <v>904.58</v>
+        <v>1004.08</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         </is>
       </c>
       <c r="H58" s="3" t="n">
-        <v>5292.11</v>
+        <v>3863.24</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="H62" s="3" t="n">
-        <v>427.81</v>
+        <v>385.03</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         </is>
       </c>
       <c r="H68" s="3" t="n">
-        <v>864.99</v>
+        <v>813.09</v>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         </is>
       </c>
       <c r="H79" s="3" t="n">
-        <v>514.0599999999999</v>
+        <v>580.89</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="H82" s="3" t="n">
-        <v>643.87</v>
+        <v>740.45</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         </is>
       </c>
       <c r="H83" s="3" t="n">
-        <v>308.54</v>
+        <v>351.74</v>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         </is>
       </c>
       <c r="H87" s="3" t="n">
-        <v>475.69</v>
+        <v>708.78</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="H95" s="3" t="n">
-        <v>625.61</v>
+        <v>606.84</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="H96" s="3" t="n">
-        <v>471.15</v>
+        <v>442.88</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="H100" s="3" t="n">
-        <v>456.22</v>
+        <v>848.5700000000001</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="H102" s="3" t="n">
-        <v>519.0599999999999</v>
+        <v>565.78</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="H103" s="3" t="n">
-        <v>999.37</v>
+        <v>1009.36</v>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="H104" s="3" t="n">
-        <v>645.21</v>
+        <v>593.59</v>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="H106" s="3" t="n">
-        <v>625.08</v>
+        <v>612.58</v>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         </is>
       </c>
       <c r="H107" s="3" t="n">
-        <v>613.95</v>
+        <v>601.67</v>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         </is>
       </c>
       <c r="H109" s="3" t="n">
-        <v>289.03</v>
+        <v>297.7</v>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         </is>
       </c>
       <c r="H111" s="3" t="n">
-        <v>310.43</v>
+        <v>266.97</v>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="H112" s="3" t="n">
-        <v>666.74</v>
+        <v>580.0599999999999</v>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="H117" s="3" t="n">
-        <v>388.3</v>
+        <v>788.25</v>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="H119" s="3" t="n">
-        <v>709.46</v>
+        <v>773.3099999999999</v>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         </is>
       </c>
       <c r="H125" s="3" t="n">
-        <v>422.74</v>
+        <v>760.9299999999999</v>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         </is>
       </c>
       <c r="H127" s="3" t="n">
-        <v>812.27</v>
+        <v>1510.82</v>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         </is>
       </c>
       <c r="H129" s="3" t="n">
-        <v>2177.85</v>
+        <v>1176.04</v>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="H130" s="3" t="n">
-        <v>1127.74</v>
+        <v>969.86</v>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="H132" s="3" t="n">
-        <v>212.69</v>
+        <v>238.21</v>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         </is>
       </c>
       <c r="H133" s="3" t="n">
-        <v>239.6</v>
+        <v>206.06</v>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         </is>
       </c>
       <c r="H134" s="3" t="n">
-        <v>278.04</v>
+        <v>261.36</v>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         </is>
       </c>
       <c r="H135" s="3" t="n">
-        <v>246.38</v>
+        <v>261.16</v>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         </is>
       </c>
       <c r="H136" s="3" t="n">
-        <v>513.89</v>
+        <v>503.61</v>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         </is>
       </c>
       <c r="H137" s="3" t="n">
-        <v>381.26</v>
+        <v>724.39</v>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="H146" s="3" t="n">
-        <v>944.97</v>
+        <v>689.83</v>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         </is>
       </c>
       <c r="H147" s="3" t="n">
-        <v>1098.5</v>
+        <v>1153.42</v>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         </is>
       </c>
       <c r="H163" s="3" t="n">
-        <v>699.45</v>
+        <v>713.4400000000001</v>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         </is>
       </c>
       <c r="H164" s="3" t="n">
-        <v>665.15</v>
+        <v>591.98</v>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         </is>
       </c>
       <c r="H166" s="3" t="n">
-        <v>364.43</v>
+        <v>317.05</v>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="H171" s="3" t="n">
-        <v>415.61</v>
+        <v>843.6900000000001</v>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         </is>
       </c>
       <c r="H172" s="3" t="n">
-        <v>564.8</v>
+        <v>615.63</v>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         </is>
       </c>
       <c r="H177" s="3" t="n">
-        <v>2185.39</v>
+        <v>2360.22</v>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         </is>
       </c>
       <c r="H182" s="3" t="n">
-        <v>520.53</v>
+        <v>588.2</v>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         </is>
       </c>
       <c r="H183" s="3" t="n">
-        <v>237.42</v>
+        <v>246.92</v>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         </is>
       </c>
       <c r="H184" s="3" t="n">
-        <v>274.22</v>
+        <v>268.74</v>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         </is>
       </c>
       <c r="H185" s="3" t="n">
-        <v>654.17</v>
+        <v>647.63</v>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         </is>
       </c>
       <c r="H190" s="3" t="n">
-        <v>516.1</v>
+        <v>959.95</v>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         </is>
       </c>
       <c r="H191" s="3" t="n">
-        <v>468.98</v>
+        <v>511.19</v>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         </is>
       </c>
       <c r="H194" s="3" t="n">
-        <v>657.85</v>
+        <v>710.48</v>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         </is>
       </c>
       <c r="H195" s="3" t="n">
-        <v>425.94</v>
+        <v>391.86</v>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         </is>
       </c>
       <c r="H196" s="3" t="n">
-        <v>646.13</v>
+        <v>665.51</v>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="H197" s="3" t="n">
-        <v>377.08</v>
+        <v>433.64</v>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         </is>
       </c>
       <c r="H198" s="3" t="n">
-        <v>1039.17</v>
+        <v>1049.56</v>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         </is>
       </c>
       <c r="H199" s="3" t="n">
-        <v>279.49</v>
+        <v>282.28</v>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         </is>
       </c>
       <c r="H201" s="3" t="n">
-        <v>745.85</v>
+        <v>783.14</v>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         </is>
       </c>
       <c r="H213" s="3" t="n">
-        <v>634.91</v>
+        <v>692.05</v>
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         </is>
       </c>
       <c r="H214" s="3" t="n">
-        <v>394.54</v>
+        <v>441.88</v>
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         </is>
       </c>
       <c r="H217" s="3" t="n">
-        <v>1100.87</v>
+        <v>715.5700000000001</v>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         </is>
       </c>
       <c r="H218" s="3" t="n">
-        <v>1144.03</v>
+        <v>743.62</v>
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         </is>
       </c>
       <c r="H221" s="3" t="n">
-        <v>414.32</v>
+        <v>418.46</v>
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         </is>
       </c>
       <c r="H222" s="3" t="n">
-        <v>669.42</v>
+        <v>1358.92</v>
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         </is>
       </c>
       <c r="H223" s="3" t="n">
-        <v>266.39</v>
+        <v>306.35</v>
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="H224" s="3" t="n">
-        <v>605.12</v>
+        <v>538.5599999999999</v>
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         </is>
       </c>
       <c r="H228" s="3" t="n">
-        <v>893.21</v>
+        <v>911.0700000000001</v>
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         </is>
       </c>
       <c r="H232" s="3" t="n">
-        <v>566.36</v>
+        <v>617.33</v>
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         </is>
       </c>
       <c r="H237" s="3" t="n">
-        <v>506.58</v>
+        <v>435.66</v>
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="H238" s="3" t="n">
-        <v>569.3099999999999</v>
+        <v>575</v>
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
         </is>
       </c>
       <c r="H239" s="3" t="n">
-        <v>400.05</v>
+        <v>376.05</v>
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="H251" s="3" t="n">
-        <v>1066.21</v>
+        <v>1226.14</v>
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         </is>
       </c>
       <c r="H252" s="3" t="n">
-        <v>427.42</v>
+        <v>465.89</v>
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         </is>
       </c>
       <c r="H258" s="3" t="n">
-        <v>699.62</v>
+        <v>755.59</v>
       </c>
       <c r="I258" s="2" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="H260" s="3" t="n">
-        <v>748.95</v>
+        <v>786.4</v>
       </c>
       <c r="I260" s="2" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         </is>
       </c>
       <c r="H261" s="3" t="n">
-        <v>208.31</v>
+        <v>204.14</v>
       </c>
       <c r="I261" s="2" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         </is>
       </c>
       <c r="H263" s="3" t="n">
-        <v>494.06</v>
+        <v>266.79</v>
       </c>
       <c r="I263" s="2" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         </is>
       </c>
       <c r="H267" s="3" t="n">
-        <v>259.84</v>
+        <v>465.11</v>
       </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         </is>
       </c>
       <c r="H269" s="3" t="n">
-        <v>936.25</v>
+        <v>805.17</v>
       </c>
       <c r="I269" s="2" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         </is>
       </c>
       <c r="H281" s="3" t="n">
-        <v>553.49</v>
+        <v>525.8200000000001</v>
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         </is>
       </c>
       <c r="H282" s="3" t="n">
-        <v>674.65</v>
+        <v>735.37</v>
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
         </is>
       </c>
       <c r="H290" s="3" t="n">
-        <v>1568.08</v>
+        <v>846.76</v>
       </c>
       <c r="I290" s="2" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         </is>
       </c>
       <c r="H292" s="3" t="n">
-        <v>4411.57</v>
+        <v>3308.68</v>
       </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         </is>
       </c>
       <c r="H293" s="3" t="n">
-        <v>699.79</v>
+        <v>685.79</v>
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         </is>
       </c>
       <c r="H295" s="3" t="n">
-        <v>240.43</v>
+        <v>269.28</v>
       </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
@@ -15344,7 +15344,7 @@
         </is>
       </c>
       <c r="H298" s="3" t="n">
-        <v>203.23</v>
+        <v>182.91</v>
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
@@ -15544,7 +15544,7 @@
         </is>
       </c>
       <c r="H302" s="3" t="n">
-        <v>1529.65</v>
+        <v>1667.32</v>
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         </is>
       </c>
       <c r="H313" s="3" t="n">
-        <v>406.33</v>
+        <v>390.08</v>
       </c>
       <c r="I313" s="2" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         </is>
       </c>
       <c r="H319" s="3" t="n">
-        <v>471.91</v>
+        <v>443.6</v>
       </c>
       <c r="I319" s="2" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         </is>
       </c>
       <c r="H323" s="3" t="n">
-        <v>377</v>
+        <v>674.83</v>
       </c>
       <c r="I323" s="2" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         </is>
       </c>
       <c r="H325" s="3" t="n">
-        <v>645.0700000000001</v>
+        <v>1161.13</v>
       </c>
       <c r="I325" s="2" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         </is>
       </c>
       <c r="H327" s="3" t="n">
-        <v>501.92</v>
+        <v>537.05</v>
       </c>
       <c r="I327" s="2" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         </is>
       </c>
       <c r="H328" s="3" t="n">
-        <v>580.8099999999999</v>
+        <v>604.04</v>
       </c>
       <c r="I328" s="2" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         </is>
       </c>
       <c r="H337" s="3" t="n">
-        <v>725.05</v>
+        <v>833.8099999999999</v>
       </c>
       <c r="I337" s="2" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         </is>
       </c>
       <c r="H341" s="3" t="n">
-        <v>375.87</v>
+        <v>334.52</v>
       </c>
       <c r="I341" s="2" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         </is>
       </c>
       <c r="H344" s="3" t="n">
-        <v>513.8</v>
+        <v>508.66</v>
       </c>
       <c r="I344" s="2" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         </is>
       </c>
       <c r="H348" s="3" t="n">
-        <v>714.28</v>
+        <v>778.5700000000001</v>
       </c>
       <c r="I348" s="2" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         </is>
       </c>
       <c r="H350" s="3" t="n">
-        <v>1125.65</v>
+        <v>2217.53</v>
       </c>
       <c r="I350" s="2" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         </is>
       </c>
       <c r="H351" s="3" t="n">
-        <v>558.74</v>
+        <v>581.09</v>
       </c>
       <c r="I351" s="2" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         </is>
       </c>
       <c r="H352" s="3" t="n">
-        <v>312.06</v>
+        <v>346.39</v>
       </c>
       <c r="I352" s="2" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         </is>
       </c>
       <c r="H355" s="3" t="n">
-        <v>561.09</v>
+        <v>611.59</v>
       </c>
       <c r="I355" s="2" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         </is>
       </c>
       <c r="H357" s="3" t="n">
-        <v>579.83</v>
+        <v>423.28</v>
       </c>
       <c r="I357" s="2" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         </is>
       </c>
       <c r="H364" s="3" t="n">
-        <v>609.29</v>
+        <v>889.5599999999999</v>
       </c>
       <c r="I364" s="2" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         </is>
       </c>
       <c r="H369" s="3" t="n">
-        <v>574.58</v>
+        <v>597.5599999999999</v>
       </c>
       <c r="I369" s="2" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         </is>
       </c>
       <c r="H374" s="3" t="n">
-        <v>661.72</v>
+        <v>575.7</v>
       </c>
       <c r="I374" s="2" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         </is>
       </c>
       <c r="H375" s="3" t="n">
-        <v>487.86</v>
+        <v>443.95</v>
       </c>
       <c r="I375" s="2" t="inlineStr">
         <is>
@@ -19344,7 +19344,7 @@
         </is>
       </c>
       <c r="H378" s="3" t="n">
-        <v>464.07</v>
+        <v>533.6799999999999</v>
       </c>
       <c r="I378" s="2" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         </is>
       </c>
       <c r="H384" s="3" t="n">
-        <v>427.16</v>
+        <v>397.26</v>
       </c>
       <c r="I384" s="2" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
         </is>
       </c>
       <c r="H385" s="3" t="n">
-        <v>510.43</v>
+        <v>576.79</v>
       </c>
       <c r="I385" s="2" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="H387" s="3" t="n">
-        <v>292.4</v>
+        <v>584.8</v>
       </c>
       <c r="I387" s="2" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         </is>
       </c>
       <c r="H391" s="3" t="n">
-        <v>462.55</v>
+        <v>439.42</v>
       </c>
       <c r="I391" s="2" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         </is>
       </c>
       <c r="H392" s="3" t="n">
-        <v>972.28</v>
+        <v>982</v>
       </c>
       <c r="I392" s="2" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         </is>
       </c>
       <c r="H396" s="3" t="n">
-        <v>663.92</v>
+        <v>431.55</v>
       </c>
       <c r="I396" s="2" t="inlineStr">
         <is>
@@ -20294,7 +20294,7 @@
         </is>
       </c>
       <c r="H397" s="3" t="n">
-        <v>602.27</v>
+        <v>650.45</v>
       </c>
       <c r="I397" s="2" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         </is>
       </c>
       <c r="H401" s="3" t="n">
-        <v>241.03</v>
+        <v>489.29</v>
       </c>
       <c r="I401" s="2" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         </is>
       </c>
       <c r="H403" s="3" t="n">
-        <v>509.67</v>
+        <v>550.4400000000001</v>
       </c>
       <c r="I403" s="2" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         </is>
       </c>
       <c r="H405" s="3" t="n">
-        <v>222.96</v>
+        <v>443.69</v>
       </c>
       <c r="I405" s="2" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         </is>
       </c>
       <c r="H408" s="3" t="n">
-        <v>2218.72</v>
+        <v>1198.11</v>
       </c>
       <c r="I408" s="2" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         </is>
       </c>
       <c r="H419" s="3" t="n">
-        <v>1896.03</v>
+        <v>2066.67</v>
       </c>
       <c r="I419" s="2" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         </is>
       </c>
       <c r="H420" s="3" t="n">
-        <v>1030.56</v>
+        <v>1082.09</v>
       </c>
       <c r="I420" s="2" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         </is>
       </c>
       <c r="H423" s="3" t="n">
-        <v>2354.72</v>
+        <v>2566.64</v>
       </c>
       <c r="I423" s="2" t="inlineStr">
         <is>
@@ -21644,7 +21644,7 @@
         </is>
       </c>
       <c r="H424" s="3" t="n">
-        <v>590.9299999999999</v>
+        <v>626.39</v>
       </c>
       <c r="I424" s="2" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         </is>
       </c>
       <c r="H426" s="3" t="n">
-        <v>380.05</v>
+        <v>376.25</v>
       </c>
       <c r="I426" s="2" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         </is>
       </c>
       <c r="H429" s="3" t="n">
-        <v>661.22</v>
+        <v>641.38</v>
       </c>
       <c r="I429" s="2" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         </is>
       </c>
       <c r="H430" s="3" t="n">
-        <v>226.93</v>
+        <v>213.31</v>
       </c>
       <c r="I430" s="2" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         </is>
       </c>
       <c r="H433" s="3" t="n">
-        <v>878.78</v>
+        <v>887.5700000000001</v>
       </c>
       <c r="I433" s="2" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         </is>
       </c>
       <c r="H436" s="3" t="n">
-        <v>256.15</v>
+        <v>276.64</v>
       </c>
       <c r="I436" s="2" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         </is>
       </c>
       <c r="H439" s="3" t="n">
-        <v>215.79</v>
+        <v>116.53</v>
       </c>
       <c r="I439" s="2" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         </is>
       </c>
       <c r="H442" s="3" t="n">
-        <v>1592.63</v>
+        <v>1783.75</v>
       </c>
       <c r="I442" s="2" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         </is>
       </c>
       <c r="H450" s="3" t="n">
-        <v>604.8099999999999</v>
+        <v>562.47</v>
       </c>
       <c r="I450" s="2" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         </is>
       </c>
       <c r="H454" s="3" t="n">
-        <v>590.1</v>
+        <v>1292.32</v>
       </c>
       <c r="I454" s="2" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         </is>
       </c>
       <c r="H458" s="3" t="n">
-        <v>785.53</v>
+        <v>856.23</v>
       </c>
       <c r="I458" s="2" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         </is>
       </c>
       <c r="H459" s="3" t="n">
-        <v>1179.92</v>
+        <v>1168.12</v>
       </c>
       <c r="I459" s="2" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         </is>
       </c>
       <c r="H464" s="3" t="n">
-        <v>447.12</v>
+        <v>411.35</v>
       </c>
       <c r="I464" s="2" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         </is>
       </c>
       <c r="H468" s="3" t="n">
-        <v>241.74</v>
+        <v>439.97</v>
       </c>
       <c r="I468" s="2" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         </is>
       </c>
       <c r="H473" s="3" t="n">
-        <v>798.46</v>
+        <v>774.51</v>
       </c>
       <c r="I473" s="2" t="inlineStr">
         <is>
@@ -24744,7 +24744,7 @@
         </is>
       </c>
       <c r="H486" s="3" t="n">
-        <v>204.84</v>
+        <v>178.21</v>
       </c>
       <c r="I486" s="2" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         </is>
       </c>
       <c r="H488" s="3" t="n">
-        <v>1018.35</v>
+        <v>957.25</v>
       </c>
       <c r="I488" s="2" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
         </is>
       </c>
       <c r="H495" s="3" t="n">
-        <v>485.02</v>
+        <v>509.27</v>
       </c>
       <c r="I495" s="2" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         </is>
       </c>
       <c r="H496" s="3" t="n">
-        <v>365.82</v>
+        <v>409.72</v>
       </c>
       <c r="I496" s="2" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         </is>
       </c>
       <c r="H503" s="3" t="n">
-        <v>1101.32</v>
+        <v>1068.28</v>
       </c>
       <c r="I503" s="2" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         </is>
       </c>
       <c r="H507" s="3" t="n">
-        <v>767.99</v>
+        <v>783.35</v>
       </c>
       <c r="I507" s="2" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         </is>
       </c>
       <c r="H508" s="3" t="n">
-        <v>310.9</v>
+        <v>307.79</v>
       </c>
       <c r="I508" s="2" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         </is>
       </c>
       <c r="H510" s="3" t="n">
-        <v>491.46</v>
+        <v>530.78</v>
       </c>
       <c r="I510" s="2" t="inlineStr">
         <is>
@@ -26094,7 +26094,7 @@
         </is>
       </c>
       <c r="H513" s="3" t="n">
-        <v>680.3200000000001</v>
+        <v>693.9299999999999</v>
       </c>
       <c r="I513" s="2" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         </is>
       </c>
       <c r="H516" s="3" t="n">
-        <v>306.23</v>
+        <v>346.04</v>
       </c>
       <c r="I516" s="2" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         </is>
       </c>
       <c r="H522" s="3" t="n">
-        <v>578.9299999999999</v>
+        <v>567.35</v>
       </c>
       <c r="I522" s="2" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         </is>
       </c>
       <c r="H524" s="3" t="n">
-        <v>2339.58</v>
+        <v>2643.73</v>
       </c>
       <c r="I524" s="2" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         </is>
       </c>
       <c r="H536" s="3" t="n">
-        <v>316.26</v>
+        <v>170.78</v>
       </c>
       <c r="I536" s="2" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         </is>
       </c>
       <c r="H540" s="3" t="n">
-        <v>596.51</v>
+        <v>590.54</v>
       </c>
       <c r="I540" s="2" t="inlineStr">
         <is>
@@ -27494,7 +27494,7 @@
         </is>
       </c>
       <c r="H541" s="3" t="n">
-        <v>1708.06</v>
+        <v>1913.03</v>
       </c>
       <c r="I541" s="2" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         </is>
       </c>
       <c r="H542" s="3" t="n">
-        <v>312.12</v>
+        <v>293.39</v>
       </c>
       <c r="I542" s="2" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         </is>
       </c>
       <c r="H543" s="3" t="n">
-        <v>563.89</v>
+        <v>541.33</v>
       </c>
       <c r="I543" s="2" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         </is>
       </c>
       <c r="H550" s="3" t="n">
-        <v>634.38</v>
+        <v>685.13</v>
       </c>
       <c r="I550" s="2" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         </is>
       </c>
       <c r="H554" s="3" t="n">
-        <v>301.5</v>
+        <v>292.45</v>
       </c>
       <c r="I554" s="2" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         </is>
       </c>
       <c r="H555" s="3" t="n">
-        <v>348.85</v>
+        <v>320.94</v>
       </c>
       <c r="I555" s="2" t="inlineStr">
         <is>
@@ -28244,7 +28244,7 @@
         </is>
       </c>
       <c r="H556" s="3" t="n">
-        <v>574.1</v>
+        <v>528.17</v>
       </c>
       <c r="I556" s="2" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         </is>
       </c>
       <c r="H557" s="3" t="n">
-        <v>6248.57</v>
+        <v>6623.48</v>
       </c>
       <c r="I557" s="2" t="inlineStr">
         <is>
@@ -28394,7 +28394,7 @@
         </is>
       </c>
       <c r="H559" s="3" t="n">
-        <v>207.81</v>
+        <v>203.65</v>
       </c>
       <c r="I559" s="2" t="inlineStr">
         <is>
@@ -29244,7 +29244,7 @@
         </is>
       </c>
       <c r="H576" s="3" t="n">
-        <v>667.22</v>
+        <v>974.14</v>
       </c>
       <c r="I576" s="2" t="inlineStr">
         <is>
@@ -29294,7 +29294,7 @@
         </is>
       </c>
       <c r="H577" s="3" t="n">
-        <v>1176.72</v>
+        <v>1247.32</v>
       </c>
       <c r="I577" s="2" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         </is>
       </c>
       <c r="H579" s="3" t="n">
-        <v>617.12</v>
+        <v>610.95</v>
       </c>
       <c r="I579" s="2" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         </is>
       </c>
       <c r="H585" s="3" t="n">
-        <v>501.54</v>
+        <v>451.39</v>
       </c>
       <c r="I585" s="2" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         </is>
       </c>
       <c r="H590" s="3" t="n">
-        <v>355.41</v>
+        <v>316.31</v>
       </c>
       <c r="I590" s="2" t="inlineStr">
         <is>
@@ -30044,7 +30044,7 @@
         </is>
       </c>
       <c r="H592" s="3" t="n">
-        <v>457.08</v>
+        <v>342.81</v>
       </c>
       <c r="I592" s="2" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         </is>
       </c>
       <c r="H593" s="3" t="n">
-        <v>699.6900000000001</v>
+        <v>748.67</v>
       </c>
       <c r="I593" s="2" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         </is>
       </c>
       <c r="H597" s="3" t="n">
-        <v>488.16</v>
+        <v>478.4</v>
       </c>
       <c r="I597" s="2" t="inlineStr">
         <is>
@@ -30444,7 +30444,7 @@
         </is>
       </c>
       <c r="H600" s="3" t="n">
-        <v>247.96</v>
+        <v>230.6</v>
       </c>
       <c r="I600" s="2" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         </is>
       </c>
       <c r="H608" s="3" t="n">
-        <v>2175.3</v>
+        <v>2436.34</v>
       </c>
       <c r="I608" s="2" t="inlineStr">
         <is>
@@ -30994,7 +30994,7 @@
         </is>
       </c>
       <c r="H611" s="3" t="n">
-        <v>704.3099999999999</v>
+        <v>767.7</v>
       </c>
       <c r="I611" s="2" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         </is>
       </c>
       <c r="H616" s="3" t="n">
-        <v>642.0599999999999</v>
+        <v>699.85</v>
       </c>
       <c r="I616" s="2" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         </is>
       </c>
       <c r="H618" s="3" t="n">
-        <v>262.91</v>
+        <v>268.17</v>
       </c>
       <c r="I618" s="2" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         </is>
       </c>
       <c r="H619" s="3" t="n">
-        <v>897.5</v>
+        <v>816.73</v>
       </c>
       <c r="I619" s="2" t="inlineStr">
         <is>
@@ -31444,7 +31444,7 @@
         </is>
       </c>
       <c r="H620" s="3" t="n">
-        <v>201.54</v>
+        <v>205.57</v>
       </c>
       <c r="I620" s="2" t="inlineStr">
         <is>
@@ -31544,7 +31544,7 @@
         </is>
       </c>
       <c r="H622" s="3" t="n">
-        <v>1659.22</v>
+        <v>1858.33</v>
       </c>
       <c r="I622" s="2" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         </is>
       </c>
       <c r="H623" s="3" t="n">
-        <v>743.1</v>
+        <v>824.84</v>
       </c>
       <c r="I623" s="2" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         </is>
       </c>
       <c r="H624" s="3" t="n">
-        <v>406.09</v>
+        <v>377.66</v>
       </c>
       <c r="I624" s="2" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         </is>
       </c>
       <c r="H625" s="3" t="n">
-        <v>340.92</v>
+        <v>368.19</v>
       </c>
       <c r="I625" s="2" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         </is>
       </c>
       <c r="H627" s="3" t="n">
-        <v>918.63</v>
+        <v>863.51</v>
       </c>
       <c r="I627" s="2" t="inlineStr">
         <is>
@@ -31894,7 +31894,7 @@
         </is>
       </c>
       <c r="H629" s="3" t="n">
-        <v>2202.11</v>
+        <v>1981.9</v>
       </c>
       <c r="I629" s="2" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         </is>
       </c>
       <c r="H630" s="3" t="n">
-        <v>738.8099999999999</v>
+        <v>664.9299999999999</v>
       </c>
       <c r="I630" s="2" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         </is>
       </c>
       <c r="H631" s="3" t="n">
-        <v>6486.23</v>
+        <v>6875.4</v>
       </c>
       <c r="I631" s="2" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         </is>
       </c>
       <c r="H632" s="3" t="n">
-        <v>757.79</v>
+        <v>803.26</v>
       </c>
       <c r="I632" s="2" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         </is>
       </c>
       <c r="H647" s="3" t="n">
-        <v>748.51</v>
+        <v>696.11</v>
       </c>
       <c r="I647" s="2" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         </is>
       </c>
       <c r="H649" s="3" t="n">
-        <v>473.13</v>
+        <v>515.71</v>
       </c>
       <c r="I649" s="2" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         </is>
       </c>
       <c r="H650" s="3" t="n">
-        <v>740.5599999999999</v>
+        <v>555.42</v>
       </c>
       <c r="I650" s="2" t="inlineStr">
         <is>
@@ -32994,7 +32994,7 @@
         </is>
       </c>
       <c r="H651" s="3" t="n">
-        <v>588.42</v>
+        <v>594.3</v>
       </c>
       <c r="I651" s="2" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         </is>
       </c>
       <c r="H656" s="3" t="n">
-        <v>883.2</v>
+        <v>1739.9</v>
       </c>
       <c r="I656" s="2" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         </is>
       </c>
       <c r="H664" s="3" t="n">
-        <v>615.39</v>
+        <v>683.08</v>
       </c>
       <c r="I664" s="2" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         </is>
       </c>
       <c r="H667" s="3" t="n">
-        <v>654.1</v>
+        <v>614.85</v>
       </c>
       <c r="I667" s="2" t="inlineStr">
         <is>
@@ -33844,7 +33844,7 @@
         </is>
       </c>
       <c r="H668" s="3" t="n">
-        <v>920.8200000000001</v>
+        <v>1593.02</v>
       </c>
       <c r="I668" s="2" t="inlineStr">
         <is>
@@ -33994,7 +33994,7 @@
         </is>
       </c>
       <c r="H671" s="3" t="n">
-        <v>549.88</v>
+        <v>599.37</v>
       </c>
       <c r="I671" s="2" t="inlineStr">
         <is>
@@ -34044,7 +34044,7 @@
         </is>
       </c>
       <c r="H672" s="3" t="n">
-        <v>671.15</v>
+        <v>698</v>
       </c>
       <c r="I672" s="2" t="inlineStr">
         <is>
@@ -34094,7 +34094,7 @@
         </is>
       </c>
       <c r="H673" s="3" t="n">
-        <v>362.66</v>
+        <v>355.41</v>
       </c>
       <c r="I673" s="2" t="inlineStr">
         <is>
@@ -34244,7 +34244,7 @@
         </is>
       </c>
       <c r="H676" s="3" t="n">
-        <v>903.34</v>
+        <v>876.24</v>
       </c>
       <c r="I676" s="2" t="inlineStr">
         <is>
@@ -34294,7 +34294,7 @@
         </is>
       </c>
       <c r="H677" s="3" t="n">
-        <v>222.97</v>
+        <v>225.2</v>
       </c>
       <c r="I677" s="2" t="inlineStr">
         <is>
@@ -34594,7 +34594,7 @@
         </is>
       </c>
       <c r="H683" s="3" t="n">
-        <v>344.25</v>
+        <v>337.37</v>
       </c>
       <c r="I683" s="2" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         </is>
       </c>
       <c r="H684" s="3" t="n">
-        <v>652.04</v>
+        <v>749.85</v>
       </c>
       <c r="I684" s="2" t="inlineStr">
         <is>
@@ -34694,7 +34694,7 @@
         </is>
       </c>
       <c r="H685" s="3" t="n">
-        <v>308.99</v>
+        <v>655.0599999999999</v>
       </c>
       <c r="I685" s="2" t="inlineStr">
         <is>
@@ -35044,7 +35044,7 @@
         </is>
       </c>
       <c r="H692" s="3" t="n">
-        <v>541.64</v>
+        <v>1083.28</v>
       </c>
       <c r="I692" s="2" t="inlineStr">
         <is>
@@ -35144,7 +35144,7 @@
         </is>
       </c>
       <c r="H694" s="3" t="n">
-        <v>249.31</v>
+        <v>254.3</v>
       </c>
       <c r="I694" s="2" t="inlineStr">
         <is>
@@ -35344,7 +35344,7 @@
         </is>
       </c>
       <c r="H698" s="3" t="n">
-        <v>421.76</v>
+        <v>417.54</v>
       </c>
       <c r="I698" s="2" t="inlineStr">
         <is>
@@ -35394,7 +35394,7 @@
         </is>
       </c>
       <c r="H699" s="3" t="n">
-        <v>719.72</v>
+        <v>1576.19</v>
       </c>
       <c r="I699" s="2" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         </is>
       </c>
       <c r="H702" s="3" t="n">
-        <v>559.1900000000001</v>
+        <v>631.88</v>
       </c>
       <c r="I702" s="2" t="inlineStr">
         <is>
@@ -35594,7 +35594,7 @@
         </is>
       </c>
       <c r="H703" s="3" t="n">
-        <v>316.72</v>
+        <v>291.38</v>
       </c>
       <c r="I703" s="2" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         </is>
       </c>
       <c r="H704" s="3" t="n">
-        <v>457.86</v>
+        <v>448.7</v>
       </c>
       <c r="I704" s="2" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         </is>
       </c>
       <c r="H714" s="3" t="n">
-        <v>1939.64</v>
+        <v>2114.21</v>
       </c>
       <c r="I714" s="2" t="inlineStr">
         <is>
@@ -36244,7 +36244,7 @@
         </is>
       </c>
       <c r="H716" s="3" t="n">
-        <v>662.72</v>
+        <v>596.45</v>
       </c>
       <c r="I716" s="2" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         </is>
       </c>
       <c r="H728" s="3" t="n">
-        <v>380.19</v>
+        <v>806</v>
       </c>
       <c r="I728" s="2" t="inlineStr">
         <is>
@@ -36994,7 +36994,7 @@
         </is>
       </c>
       <c r="H731" s="3" t="n">
-        <v>2584.05</v>
+        <v>2325.65</v>
       </c>
       <c r="I731" s="2" t="inlineStr">
         <is>
@@ -37044,7 +37044,7 @@
         </is>
       </c>
       <c r="H732" s="3" t="n">
-        <v>997.4</v>
+        <v>1077.19</v>
       </c>
       <c r="I732" s="2" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         </is>
       </c>
       <c r="H734" s="3" t="n">
-        <v>504.61</v>
+        <v>499.56</v>
       </c>
       <c r="I734" s="2" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         </is>
       </c>
       <c r="H735" s="3" t="n">
-        <v>696.96</v>
+        <v>801.5</v>
       </c>
       <c r="I735" s="2" t="inlineStr">
         <is>
@@ -37494,7 +37494,7 @@
         </is>
       </c>
       <c r="H741" s="3" t="n">
-        <v>851.85</v>
+        <v>979.63</v>
       </c>
       <c r="I741" s="2" t="inlineStr">
         <is>
@@ -37544,7 +37544,7 @@
         </is>
       </c>
       <c r="H742" s="3" t="n">
-        <v>1651.93</v>
+        <v>1536.29</v>
       </c>
       <c r="I742" s="2" t="inlineStr">
         <is>
@@ -37794,7 +37794,7 @@
         </is>
       </c>
       <c r="H747" s="3" t="n">
-        <v>449.04</v>
+        <v>431.08</v>
       </c>
       <c r="I747" s="2" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         </is>
       </c>
       <c r="H750" s="3" t="n">
-        <v>574.73</v>
+        <v>327.6</v>
       </c>
       <c r="I750" s="2" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         </is>
       </c>
       <c r="H753" s="3" t="n">
-        <v>273.37</v>
+        <v>246.03</v>
       </c>
       <c r="I753" s="2" t="inlineStr">
         <is>
@@ -38194,7 +38194,7 @@
         </is>
       </c>
       <c r="H755" s="3" t="n">
-        <v>962.42</v>
+        <v>981.67</v>
       </c>
       <c r="I755" s="2" t="inlineStr">
         <is>
@@ -38244,7 +38244,7 @@
         </is>
       </c>
       <c r="H756" s="3" t="n">
-        <v>731.48</v>
+        <v>672.96</v>
       </c>
       <c r="I756" s="2" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         </is>
       </c>
       <c r="H757" s="3" t="n">
-        <v>480.57</v>
+        <v>514.21</v>
       </c>
       <c r="I757" s="2" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         </is>
       </c>
       <c r="H759" s="3" t="n">
-        <v>679.8099999999999</v>
+        <v>1420.8</v>
       </c>
       <c r="I759" s="2" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         </is>
       </c>
       <c r="H761" s="3" t="n">
-        <v>337.1</v>
+        <v>340.47</v>
       </c>
       <c r="I761" s="2" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         </is>
       </c>
       <c r="H765" s="3" t="n">
-        <v>505.18</v>
+        <v>535.49</v>
       </c>
       <c r="I765" s="2" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         </is>
       </c>
       <c r="H766" s="3" t="n">
-        <v>539.8200000000001</v>
+        <v>1074.24</v>
       </c>
       <c r="I766" s="2" t="inlineStr">
         <is>
@@ -38894,7 +38894,7 @@
         </is>
       </c>
       <c r="H769" s="3" t="n">
-        <v>375.6</v>
+        <v>379.36</v>
       </c>
       <c r="I769" s="2" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         </is>
       </c>
       <c r="H770" s="3" t="n">
-        <v>334.09</v>
+        <v>287.32</v>
       </c>
       <c r="I770" s="2" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         </is>
       </c>
       <c r="H777" s="3" t="n">
-        <v>768.6799999999999</v>
+        <v>837.86</v>
       </c>
       <c r="I777" s="2" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         </is>
       </c>
       <c r="H778" s="3" t="n">
-        <v>413.33</v>
+        <v>223.2</v>
       </c>
       <c r="I778" s="2" t="inlineStr">
         <is>
@@ -39394,7 +39394,7 @@
         </is>
       </c>
       <c r="H779" s="3" t="n">
-        <v>401.15</v>
+        <v>453.3</v>
       </c>
       <c r="I779" s="2" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         </is>
       </c>
       <c r="H794" s="3" t="n">
-        <v>598.02</v>
+        <v>1136.24</v>
       </c>
       <c r="I794" s="2" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         </is>
       </c>
       <c r="H804" s="3" t="n">
-        <v>726.4400000000001</v>
+        <v>697.38</v>
       </c>
       <c r="I804" s="2" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         </is>
       </c>
       <c r="H808" s="3" t="n">
-        <v>1022.22</v>
+        <v>930.22</v>
       </c>
       <c r="I808" s="2" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         </is>
       </c>
       <c r="H816" s="3" t="n">
-        <v>364.62</v>
+        <v>386.5</v>
       </c>
       <c r="I816" s="2" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         </is>
       </c>
       <c r="H817" s="3" t="n">
-        <v>596.98</v>
+        <v>591.01</v>
       </c>
       <c r="I817" s="2" t="inlineStr">
         <is>
@@ -41344,7 +41344,7 @@
         </is>
       </c>
       <c r="H818" s="3" t="n">
-        <v>635.55</v>
+        <v>362.26</v>
       </c>
       <c r="I818" s="2" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         </is>
       </c>
       <c r="H819" s="3" t="n">
-        <v>955.65</v>
+        <v>821.86</v>
       </c>
       <c r="I819" s="2" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         </is>
       </c>
       <c r="H824" s="3" t="n">
-        <v>2786.74</v>
+        <v>2508.07</v>
       </c>
       <c r="I824" s="2" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         </is>
       </c>
       <c r="H826" s="3" t="n">
-        <v>280.18</v>
+        <v>274.58</v>
       </c>
       <c r="I826" s="2" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         </is>
       </c>
       <c r="H834" s="3" t="n">
-        <v>713.74</v>
+        <v>463.93</v>
       </c>
       <c r="I834" s="2" t="inlineStr">
         <is>
@@ -42394,7 +42394,7 @@
         </is>
       </c>
       <c r="H839" s="3" t="n">
-        <v>705.3</v>
+        <v>634.77</v>
       </c>
       <c r="I839" s="2" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         </is>
       </c>
       <c r="H845" s="3" t="n">
-        <v>395.36</v>
+        <v>399.31</v>
       </c>
       <c r="I845" s="2" t="inlineStr">
         <is>
@@ -42794,7 +42794,7 @@
         </is>
       </c>
       <c r="H847" s="3" t="n">
-        <v>2194.66</v>
+        <v>1185.12</v>
       </c>
       <c r="I847" s="2" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         </is>
       </c>
       <c r="H848" s="3" t="n">
-        <v>308.19</v>
+        <v>277.37</v>
       </c>
       <c r="I848" s="2" t="inlineStr">
         <is>
@@ -42944,7 +42944,7 @@
         </is>
       </c>
       <c r="H850" s="3" t="n">
-        <v>510.76</v>
+        <v>480.11</v>
       </c>
       <c r="I850" s="2" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         </is>
       </c>
       <c r="H855" s="3" t="n">
-        <v>1587.47</v>
+        <v>1730.34</v>
       </c>
       <c r="I855" s="2" t="inlineStr">
         <is>
@@ -43294,7 +43294,7 @@
         </is>
       </c>
       <c r="H857" s="3" t="n">
-        <v>527.58</v>
+        <v>490.65</v>
       </c>
       <c r="I857" s="2" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         </is>
       </c>
       <c r="H858" s="3" t="n">
-        <v>256.2</v>
+        <v>248.51</v>
       </c>
       <c r="I858" s="2" t="inlineStr">
         <is>
@@ -43494,7 +43494,7 @@
         </is>
       </c>
       <c r="H861" s="3" t="n">
-        <v>893.55</v>
+        <v>866.74</v>
       </c>
       <c r="I861" s="2" t="inlineStr">
         <is>
@@ -43894,7 +43894,7 @@
         </is>
       </c>
       <c r="H869" s="3" t="n">
-        <v>2124</v>
+        <v>2102.76</v>
       </c>
       <c r="I869" s="2" t="inlineStr">
         <is>
@@ -43944,7 +43944,7 @@
         </is>
       </c>
       <c r="H870" s="3" t="n">
-        <v>745.67</v>
+        <v>1334.75</v>
       </c>
       <c r="I870" s="2" t="inlineStr">
         <is>
@@ -44194,7 +44194,7 @@
         </is>
       </c>
       <c r="H875" s="3" t="n">
-        <v>2128.7</v>
+        <v>2107.41</v>
       </c>
       <c r="I875" s="2" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         </is>
       </c>
       <c r="H883" s="3" t="n">
-        <v>331.78</v>
+        <v>301.92</v>
       </c>
       <c r="I883" s="2" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         </is>
       </c>
       <c r="H885" s="3" t="n">
-        <v>1822.82</v>
+        <v>1804.59</v>
       </c>
       <c r="I885" s="2" t="inlineStr">
         <is>
@@ -44744,7 +44744,7 @@
         </is>
       </c>
       <c r="H886" s="3" t="n">
-        <v>1043.32</v>
+        <v>938.99</v>
       </c>
       <c r="I886" s="2" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         </is>
       </c>
       <c r="H887" s="3" t="n">
-        <v>1142.11</v>
+        <v>833.74</v>
       </c>
       <c r="I887" s="2" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         </is>
       </c>
       <c r="H888" s="3" t="n">
-        <v>1082.14</v>
+        <v>1244.46</v>
       </c>
       <c r="I888" s="2" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         </is>
       </c>
       <c r="H889" s="3" t="n">
-        <v>489.48</v>
+        <v>499.27</v>
       </c>
       <c r="I889" s="2" t="inlineStr">
         <is>
@@ -45044,7 +45044,7 @@
         </is>
       </c>
       <c r="H892" s="3" t="n">
-        <v>654.0599999999999</v>
+        <v>712.9299999999999</v>
       </c>
       <c r="I892" s="2" t="inlineStr">
         <is>
@@ -45094,7 +45094,7 @@
         </is>
       </c>
       <c r="H893" s="3" t="n">
-        <v>1382.62</v>
+        <v>1202.88</v>
       </c>
       <c r="I893" s="2" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         </is>
       </c>
       <c r="H899" s="3" t="n">
-        <v>1146.28</v>
+        <v>1157.74</v>
       </c>
       <c r="I899" s="2" t="inlineStr">
         <is>
@@ -45402,6 +45402,3006 @@
         </is>
       </c>
       <c r="J899" s="2" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>AF-50001</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>QLD073</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>Nationwide Browns Plains</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>SN100508</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Door seal failure (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H900" t="n">
+        <v>961.47</v>
+      </c>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J900" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>AF-50002</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>WA092</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>Nationwide Mandurah</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>SN100623</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Motor overheating (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H901" t="n">
+        <v>1243.12</v>
+      </c>
+      <c r="I901" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J901" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>AF-50003</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>WA098</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>Nationwide Albany</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>SN100667</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Motor overheating (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H902" t="n">
+        <v>675.3</v>
+      </c>
+      <c r="I902" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J902" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>AF-50004</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>2023-05-05</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>NSW033</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>Nationwide Lismore</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>SN100206</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Control panel fault (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H903" t="n">
+        <v>1030.95</v>
+      </c>
+      <c r="I903" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J903" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>AF-50005</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>NSW033</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>Nationwide Lismore</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>SN100206</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Hydraulic leak (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H904" t="n">
+        <v>1076.35</v>
+      </c>
+      <c r="I904" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J904" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>AF-50006</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>NSW012</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>Nationwide Burwood</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>SN100087</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Motor overheating (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H905" t="n">
+        <v>1098.5</v>
+      </c>
+      <c r="I905" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J905" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>AF-50007</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>VIC039</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>Nationwide Craigieburn</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>SN100242</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Hydraulic leak (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H906" t="n">
+        <v>628.52</v>
+      </c>
+      <c r="I906" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J906" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>AF-50008</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>NSW009</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>Nationwide Sutherland</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>SN100054</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Hydraulic leak (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H907" t="n">
+        <v>1222.49</v>
+      </c>
+      <c r="I907" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J907" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>AF-50009</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>NSW009</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>Nationwide Sutherland</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>SN100054</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Sensor failure (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H908" t="n">
+        <v>1015.3</v>
+      </c>
+      <c r="I908" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J908" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>AF-50010</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>2023-11-10</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>NSW003</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>Nationwide Penrith</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>SN100022</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>Compactor Breakdown Repair - Door seal failure (Ironbark Compaction CP-800)</t>
+        </is>
+      </c>
+      <c r="H909" t="n">
+        <v>603.6799999999999</v>
+      </c>
+      <c r="I909" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J909" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>AF-50011</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>2025-02-15</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>NSW003</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>Nationwide Penrith</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>SN100022</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>Compactor Breakdown Repair - Belt/chain wear (Ironbark Compaction CP-800)</t>
+        </is>
+      </c>
+      <c r="H910" t="n">
+        <v>925.42</v>
+      </c>
+      <c r="I910" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J910" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>AF-50012</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>SA113</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>Nationwide Port Lincoln</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>SN100759</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Control panel fault (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H911" t="n">
+        <v>1166.25</v>
+      </c>
+      <c r="I911" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J911" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>AF-50013</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>SA113</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>Nationwide Port Lincoln</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>SN100759</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Sensor failure (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H912" t="n">
+        <v>1010.31</v>
+      </c>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J912" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>AF-50014</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>2023-01-03</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>VIC044</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>Nationwide Doncaster</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>SN100287</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Control panel fault (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H913" t="n">
+        <v>920.3200000000001</v>
+      </c>
+      <c r="I913" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J913" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>AF-50015</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>VIC044</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>Nationwide Doncaster</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>SN100287</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Control panel fault (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H914" t="n">
+        <v>1366.43</v>
+      </c>
+      <c r="I914" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J914" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>AF-50016</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>2023-11-01</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>NSW005</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>Nationwide Bankstown</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>SN100035</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Sensor failure (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H915" t="n">
+        <v>767.77</v>
+      </c>
+      <c r="I915" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J915" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>AF-50017</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>NSW005</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>Nationwide Bankstown</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>SN100035</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Electrical fault (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H916" t="n">
+        <v>1384.29</v>
+      </c>
+      <c r="I916" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J916" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>AF-50018</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>NSW005</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>Nationwide Bankstown</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>SN100035</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Control panel fault (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H917" t="n">
+        <v>1052.99</v>
+      </c>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J917" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>AF-50019</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>2023-04-25</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>VIC059</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>Nationwide Wodonga</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>SN100402</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Belt/chain wear (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H918" t="n">
+        <v>869.51</v>
+      </c>
+      <c r="I918" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J918" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>AF-50020</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>2024-05-11</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>VIC059</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>Nationwide Wodonga</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>SN100402</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Hydraulic leak (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H919" t="n">
+        <v>1371.26</v>
+      </c>
+      <c r="I919" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J919" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>AF-50021</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>VIC059</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>Nationwide Wodonga</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>SN100402</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Sensor failure (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H920" t="n">
+        <v>1165.61</v>
+      </c>
+      <c r="I920" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J920" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>AF-50022</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>2023-01-02</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>NSW032</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>Nationwide Nowra</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>SN100200</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Door seal failure (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H921" t="n">
+        <v>1237.62</v>
+      </c>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J921" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>AF-50023</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>NSW032</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>Nationwide Nowra</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>SN100200</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Sensor failure (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H922" t="n">
+        <v>957.9400000000001</v>
+      </c>
+      <c r="I922" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J922" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>AF-50024</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>2023-04-24</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>QLD072</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>Nationwide Capalaba</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>SN100494</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Motor overheating (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H923" t="n">
+        <v>935.38</v>
+      </c>
+      <c r="I923" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J923" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>AF-50025</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>QLD072</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>Nationwide Capalaba</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>SN100494</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Electrical fault (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H924" t="n">
+        <v>936.6</v>
+      </c>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J924" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>AF-50026</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>NSW017</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>Nationwide Manly</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>SN100109</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Belt/chain wear (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H925" t="n">
+        <v>1291.47</v>
+      </c>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J925" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>AF-50027</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>WA085</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>Nationwide Cannington</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>SN100579</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Hydraulic leak (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H926" t="n">
+        <v>768.5700000000001</v>
+      </c>
+      <c r="I926" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J926" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>AF-50028</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>VIC041</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>Nationwide Werribee</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>SN100262</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Control panel fault (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H927" t="n">
+        <v>633.6900000000001</v>
+      </c>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J927" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>AF-50029</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>VIC041</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>Nationwide Werribee</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>SN100262</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Door seal failure (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H928" t="n">
+        <v>806.62</v>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J928" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>AF-50030</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>NT126</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>Nationwide Alice Springs</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>SN100840</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Belt/chain wear (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H929" t="n">
+        <v>908.9400000000001</v>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J929" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>AF-50031</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>NT126</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>Nationwide Alice Springs</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>SN100840</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Sensor failure (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H930" t="n">
+        <v>1066.19</v>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J930" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>AF-50032</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>VIC055</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>Nationwide Bendigo</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>SN100381</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>Compactor Breakdown Repair - Ram jam (Ironbark Compaction CP-800)</t>
+        </is>
+      </c>
+      <c r="H931" t="n">
+        <v>897.36</v>
+      </c>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J931" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>AF-50033</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>2023-08-05</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>NSW026</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>Nationwide Orange</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>SN100165</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Door seal failure (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H932" t="n">
+        <v>1265.89</v>
+      </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J932" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>AF-50034</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>2023-03-28</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>QLD076</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>Nationwide Cairns</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>SN100520</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Electrical fault (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H933" t="n">
+        <v>746.26</v>
+      </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J933" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>AF-50035</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>2023-03-10</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>WA087</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>Nationwide Fremantle</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>SN100592</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Sensor failure (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H934" t="n">
+        <v>1254.24</v>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J934" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>AF-50036</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>2023-04-24</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>NSW008</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>Nationwide Campbelltown</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>SN100050</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Sensor failure (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H935" t="n">
+        <v>726.78</v>
+      </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J935" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>AF-50037</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>NSW008</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>Nationwide Campbelltown</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>SN100050</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Sensor failure (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H936" t="n">
+        <v>1149.58</v>
+      </c>
+      <c r="I936" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J936" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>AF-50038</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>2023-07-16</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>NSW004</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>Nationwide Liverpool</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>SN100030</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Control panel fault (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H937" t="n">
+        <v>937.17</v>
+      </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J937" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>AF-50039</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>2023-02-04</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>NT125</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>Nationwide Palmerston</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>SN100834</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Hydraulic leak (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H938" t="n">
+        <v>1009.88</v>
+      </c>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J938" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>AF-50040</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>NT125</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>Nationwide Palmerston</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>SN100834</t>
+        </is>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Electrical fault (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H939" t="n">
+        <v>805.59</v>
+      </c>
+      <c r="I939" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J939" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>AF-50041</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>QLD079</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>Nationwide Rockhampton</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>SN100542</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Belt/chain wear (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H940" t="n">
+        <v>1016.06</v>
+      </c>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J940" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>AF-50042</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>QLD079</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>Nationwide Rockhampton</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>SN100542</t>
+        </is>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Motor overheating (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H941" t="n">
+        <v>782.72</v>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J941" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>AF-50043</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>VIC060</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>Nationwide Traralgon</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>SN100406</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Control panel fault (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H942" t="n">
+        <v>824.1799999999999</v>
+      </c>
+      <c r="I942" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J942" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>AF-50044</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>VIC060</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>Nationwide Traralgon</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>SN100406</t>
+        </is>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Hydraulic leak (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H943" t="n">
+        <v>655.3200000000001</v>
+      </c>
+      <c r="I943" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J943" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>AF-50045</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>SA101</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>Nationwide Elizabeth</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>SN100687</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Sensor failure (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H944" t="n">
+        <v>648.36</v>
+      </c>
+      <c r="I944" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J944" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>AF-50046</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>2023-03-10</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>QLD075</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>Nationwide Toowoomba</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>SN100515</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Ram jam (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H945" t="n">
+        <v>1024.8</v>
+      </c>
+      <c r="I945" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J945" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>AF-50047</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>2023-03-03</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>SA111</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>Nationwide Whyalla</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>SN100742</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Ram jam (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H946" t="n">
+        <v>710.73</v>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J946" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>AF-50048</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>SA111</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>Nationwide Whyalla</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>SN100742</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Motor overheating (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H947" t="n">
+        <v>1071.9</v>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J947" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>AF-50049</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>2023-01-16</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>QLD061</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>Nationwide Brisbane City</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>SN100412</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Ram jam (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H948" t="n">
+        <v>1160.78</v>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J948" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>AF-50050</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>QLD061</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>Nationwide Brisbane City</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>SN100412</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Control panel fault (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H949" t="n">
+        <v>985.79</v>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J949" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>AF-50051</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>2023-12-10</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>WA089</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>Nationwide Osborne Park</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>SN100602</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Ram jam (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H950" t="n">
+        <v>709.28</v>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J950" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>AF-50052</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>2023-02-03</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>VIC051</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>Nationwide Footscray</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>SN100333</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Door seal failure (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H951" t="n">
+        <v>1036.88</v>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J951" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>AF-50053</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>2023-12-02</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>TAS118</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>Nationwide Burnie</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>SN100787</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Motor overheating (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H952" t="n">
+        <v>1234.61</v>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J952" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>AF-50054</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>SA106</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>Nationwide Prospect</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>SN100720</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Control panel fault (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H953" t="n">
+        <v>1148.12</v>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J953" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>AF-50055</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>2023-02-28</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>WA083</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>Nationwide Perth</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>SN100568</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Electrical fault (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H954" t="n">
+        <v>1355.39</v>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J954" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>AF-50056</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>2023-01-28</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>WA090</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>Nationwide Malaga</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>SN100606</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Door seal failure (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H955" t="n">
+        <v>1058.25</v>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J955" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>AF-50057</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>2023-10-22</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>NSW021</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>Nationwide Newcastle</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>SN100131</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Electrical fault (Kestrel Waste Systems BL-6500)</t>
+        </is>
+      </c>
+      <c r="H956" t="n">
+        <v>903.34</v>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J956" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>AF-50058</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>2023-01-20</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>QLD066</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>Nationwide Southport</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>SN100446</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Control panel fault (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H957" t="n">
+        <v>664.16</v>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J957" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>AF-50059</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>QLD066</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>Nationwide Southport</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>SN100446</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Belt/chain wear (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H958" t="n">
+        <v>1303.83</v>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J958" t="inlineStr">
+        <is>
+          <t>Breakdown Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>AF-50060</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>2023-12-11</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>Nationwide Supply Co.</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>VIC056</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>Nationwide Shepparton</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>SN100385</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>Baler Breakdown Repair - Electrical fault (Kestrel Waste Systems BL-4000)</t>
+        </is>
+      </c>
+      <c r="H959" t="n">
+        <v>1347.4</v>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="J959" t="inlineStr">
         <is>
           <t>Breakdown Repair</t>
         </is>
